--- a/Jalpa_Index_Match Assignment Task.xlsx
+++ b/Jalpa_Index_Match Assignment Task.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Library1\Desktop\Jalpa Assignment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Library5\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{697830F6-FC03-4A5D-9FE4-A902E3BD425D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501C436F-B45B-4C63-B2B1-16401743DD63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{9376FB01-1D26-41A8-8BEE-93AE0355172F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{9376FB01-1D26-41A8-8BEE-93AE0355172F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="159">
   <si>
     <t>Product</t>
   </si>
@@ -498,13 +498,31 @@
   </si>
   <si>
     <t>Find the Store State for S002</t>
+  </si>
+  <si>
+    <t>Beginner</t>
+  </si>
+  <si>
+    <t>Customer Lookup</t>
+  </si>
+  <si>
+    <t>Store Lookup</t>
+  </si>
+  <si>
+    <t>Sales Analysis</t>
+  </si>
+  <si>
+    <t>Task 13</t>
+  </si>
+  <si>
+    <t>Retrieve the Product Name for every Product ID in the Sales sheet.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -512,8 +530,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,6 +564,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -551,12 +589,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,9 +617,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -615,7 +657,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -721,7 +763,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -863,7 +905,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1127,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA753246-4BC5-4670-BECA-4D001A2C302F}">
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1135,311 +1177,364 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="5" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="6"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>125</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="3" t="str">
-        <f>INDEX(Sheet1!D1:D12,MATCH(Answers!B5,Sheet1!B1:B12,0))</f>
+      <c r="C6" s="3" t="str">
+        <f>INDEX(Sheet1!D1:D12,MATCH(Answers!B6,Sheet1!B1:B12,0))</f>
         <v>Printer</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>130</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="3">
-        <f>INDEX(Sheet1!G1:G12,MATCH(Answers!B10,Sheet1!B1:B12,0))</f>
+      <c r="C11" s="3">
+        <f>INDEX(Sheet1!G1:G12,MATCH(Answers!B11,Sheet1!B1:B12,0))</f>
         <v>12000</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>133</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="3" t="str">
-        <f>INDEX(Sheet1!F1:F12,MATCH(Answers!B15,Sheet1!B1:B12,0))</f>
+      <c r="C16" s="3" t="str">
+        <f>INDEX(Sheet1!F1:F12,MATCH(Answers!B16,Sheet1!B1:B12,0))</f>
         <v>Sony</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>135</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C20" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="3">
-        <f>INDEX(Sheet1!H1:H12,MATCH(Answers!B20,Sheet1!B1:B12,0))</f>
+      <c r="C21" s="3">
+        <f>INDEX(Sheet1!H1:H12,MATCH(Answers!B21,Sheet1!B1:B12,0))</f>
         <v>120</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="22" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>137</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B24" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C26" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="2" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="3" t="str">
-        <f>INDEX(Sheet1!E1:E12,MATCH(Answers!B25,Sheet1!B1:B12,0))</f>
+      <c r="C27" s="3" t="str">
+        <f>INDEX(Sheet1!E1:E12,MATCH(Answers!B27,Sheet1!B1:B12,0))</f>
         <v>Accessories</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    <row r="28" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" s="6"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>139</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B31" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="4" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C33" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="3" t="str">
-        <f>INDEX(Sheet2!B1:B12,MATCH(Answers!B30,Sheet2!A1:A12,0))</f>
+      <c r="C34" s="3" t="str">
+        <f>INDEX(Sheet2!B1:B12,MATCH(Answers!B34,Sheet2!A1:A12,0))</f>
         <v>Rohan Gupta</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>141</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B36" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B34" s="4" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C38" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="2" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="3" t="str">
-        <f>INDEX(Sheet2!C6:C17,MATCH(Answers!B35,Sheet2!A6:A17,0))</f>
+      <c r="C39" s="3" t="str">
+        <f>INDEX(Sheet2!C6:C17,MATCH(Answers!B39,Sheet2!A6:A17,0))</f>
         <v>Kochi</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>143</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B41" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B39" s="4" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C43" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="3" t="str">
-        <f>INDEX(Sheet2!D1:D12,MATCH(Answers!B40,Sheet2!A1:A12,0))</f>
+      <c r="C44" s="3" t="str">
+        <f>INDEX(Sheet2!D1:D12,MATCH(Answers!B44,Sheet2!A1:A12,0))</f>
         <v>Maharashtra</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>145</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B46" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B44" s="4" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C48" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C45" s="3" t="str">
-        <f>INDEX(Sheet2!E6:E17,MATCH(Answers!B45,Sheet2!A6:A17,0))</f>
+      <c r="C49" s="3" t="str">
+        <f>INDEX(Sheet2!E6:E17,MATCH(Answers!B49,Sheet2!A6:A17,0))</f>
         <v>Female</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    <row r="50" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="B51" s="6"/>
+    </row>
+    <row r="52" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>147</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B53" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B49" s="4" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C55" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C50" s="3" t="str">
-        <f>INDEX(Sheet3!B1:B7,MATCH(Answers!B50,Sheet3!A1:A7,0))</f>
+      <c r="C56" s="3" t="str">
+        <f>INDEX(Sheet3!B1:B7,MATCH(Answers!B56,Sheet3!A1:A7,0))</f>
         <v>Central Store</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>149</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B58" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B54" s="4" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C60" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B55" s="2" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C55" s="3" t="str">
-        <f>INDEX(Sheet3!C6:C12,MATCH(Answers!B55,Sheet3!A6:A12,0))</f>
+      <c r="C61" s="3" t="str">
+        <f>INDEX(Sheet3!C6:C12,MATCH(Answers!B61,Sheet3!A6:A12,0))</f>
         <v>Jaipur</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>151</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B63" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B59" s="4" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C65" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C60" s="3" t="str">
-        <f>INDEX(Sheet3!D1:D7,MATCH(Answers!B60,Sheet3!A1:A7,0))</f>
+      <c r="C66" s="3" t="str">
+        <f>INDEX(Sheet3!D1:D7,MATCH(Answers!B66,Sheet3!A1:A7,0))</f>
         <v>Rajasthan</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B68" s="6"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C73" s="3" t="e">
+        <f>INDEX(Sheet3!B18:B24,MATCH(Answers!B73,Sheet3!A18:A24,0))</f>
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>

--- a/Jalpa_Index_Match Assignment Task.xlsx
+++ b/Jalpa_Index_Match Assignment Task.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Library5\OneDrive\Desktop\Jalpa Assignments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Library1\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E40F779A-A862-48C4-8774-037BF249D471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20AE1775-97AF-43B7-B2E6-37D27393EAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="1" xr2:uid="{9376FB01-1D26-41A8-8BEE-93AE0355172F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9376FB01-1D26-41A8-8BEE-93AE0355172F}"/>
   </bookViews>
   <sheets>
     <sheet name="Product" sheetId="1" r:id="rId1"/>
     <sheet name="Answers" sheetId="5" r:id="rId2"/>
-    <sheet name="Customer" sheetId="2" r:id="rId3"/>
-    <sheet name="Store" sheetId="3" r:id="rId4"/>
-    <sheet name="Sale" sheetId="4" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId3"/>
+    <sheet name="Customer" sheetId="2" r:id="rId4"/>
+    <sheet name="Store" sheetId="3" r:id="rId5"/>
+    <sheet name="Sale" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="213">
   <si>
     <t>Product</t>
   </si>
@@ -607,6 +608,99 @@
   </si>
   <si>
     <t>Display: - Product Name - Category - Brand - Customer Name - Customer City - Store Name - Store City - Quantity - Product Price - Total Sales - Date</t>
+  </si>
+  <si>
+    <t>┌──────────────────────────────────────────────────────────────┐</t>
+  </si>
+  <si>
+    <t>│              TRANSACTION DETAILS DASHBOARD                   │</t>
+  </si>
+  <si>
+    <t>├──────────────────────────────────────────────────────────────┤</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Enter Sale ID:   [ SA008 ]        ← User Input</t>
+  </si>
+  <si>
+    <t>────────────────────────────────────────────────────────────────</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Transaction Information</t>
+  </si>
+  <si>
+    <t>┌───────────────────────┬──────────────────────────────┐</t>
+  </si>
+  <si>
+    <t>│ Sale ID               │ SA008                        │</t>
+  </si>
+  <si>
+    <t>│ Date                  │ 08-Jan-2026                  │</t>
+  </si>
+  <si>
+    <t>│ Quantity              │ 2                            │</t>
+  </si>
+  <si>
+    <t>│ Product Price         │ ₹3,500                       │</t>
+  </si>
+  <si>
+    <t>│ Total Sales           │ ₹7,000                       │</t>
+  </si>
+  <si>
+    <t>└───────────────────────┴──────────────────────────────┘</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Product Information</t>
+  </si>
+  <si>
+    <t>│ Product ID            │ P1010                        │</t>
+  </si>
+  <si>
+    <t>│ Product Name          │ Webcam                       │</t>
+  </si>
+  <si>
+    <t>│ Category              │ Accessories                  │</t>
+  </si>
+  <si>
+    <t>│ Brand                 │ Logitech                     │</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Customer Information</t>
+  </si>
+  <si>
+    <t>│ Customer ID           │ C008                         │</t>
+  </si>
+  <si>
+    <t>│ Customer Name         │ Pooja Sharma                 │</t>
+  </si>
+  <si>
+    <t>│ City                  │ Lucknow                      │</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Store Information</t>
+  </si>
+  <si>
+    <t>│ Store ID              │ S003                         │</t>
+  </si>
+  <si>
+    <t>│ Store Name            │ Central Store                │</t>
+  </si>
+  <si>
+    <t>│ Store City            │ Mumbai                       │</t>
+  </si>
+  <si>
+    <t>Transaction Detail Dashboard</t>
+  </si>
+  <si>
+    <t>Transaction Information</t>
+  </si>
+  <si>
+    <t>Product Information</t>
+  </si>
+  <si>
+    <t>Customer Information</t>
+  </si>
+  <si>
+    <t>Store Information</t>
   </si>
 </sst>
 </file>
@@ -686,7 +780,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -699,6 +793,8 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -717,9 +813,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -757,7 +853,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -863,7 +959,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1005,7 +1101,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1263,13 +1359,16 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Product" prompt="1_x000a_2_x000a_3_x000a_" sqref="B3:B12" xr:uid="{D35AAED9-AB6D-430F-B49D-0C86C9BEFCA3}"/>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA753246-4BC5-4670-BECA-4D001A2C302F}">
-  <dimension ref="A1:XFC117"/>
+  <dimension ref="A1:XFC148"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -10520,7 +10619,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>178</v>
       </c>
@@ -10528,14 +10627,182 @@
         <v>179</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B119" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B121" t="s">
+        <v>104</v>
+      </c>
+      <c r="C121" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B123" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B125" t="s">
+        <v>104</v>
+      </c>
+      <c r="C125" t="str">
+        <f>C121</f>
+        <v>SA015</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B126" t="s">
+        <v>108</v>
+      </c>
+      <c r="C126" s="12">
+        <f>INDEX(Sale!H2:H16,MATCH(Answers!C125,Sale!A2:A16,0))</f>
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B127" t="s">
+        <v>107</v>
+      </c>
+      <c r="C127" s="13">
+        <f>INDEX(Sale!G1:G16,MATCH(Answers!C125,Sale!A1:A16,0))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B128" t="s">
+        <v>159</v>
+      </c>
+      <c r="C128" s="13">
+        <f>INDEX(Sale!D1:D16,MATCH(Answers!C125,Sale!A1:A16,0))</f>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B129" t="s">
+        <v>170</v>
+      </c>
+      <c r="C129" s="13">
+        <f>INDEX(Sale!I1:I16,MATCH(Answers!C125,Sale!A1:A16,0))</f>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B131" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B133" t="s">
+        <v>105</v>
+      </c>
+      <c r="C133" t="str">
+        <f>INDEX(Sale!B1:B16,MATCH(Answers!C121,Sale!A1:A16,0))</f>
+        <v>P1002</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B134" t="s">
+        <v>39</v>
+      </c>
+      <c r="C134" t="str">
+        <f>INDEX(Sale!C1:C16,MATCH(Answers!C121,Sale!A1:A16,0))</f>
+        <v>Smartphone</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B135" t="s">
+        <v>2</v>
+      </c>
+      <c r="C135" t="str">
+        <f>INDEX(Product!E1:E12,MATCH(Answers!C133,Product!B1:B12,0))</f>
+        <v>Electronics</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B136" t="s">
+        <v>3</v>
+      </c>
+      <c r="C136" t="str">
+        <f>INDEX(Product!F1:F12,MATCH(Answers!C133,Product!B1:B12,0))</f>
+        <v>Samsung</v>
+      </c>
+    </row>
+    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B138" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B140" t="s">
+        <v>106</v>
+      </c>
+      <c r="C140" t="str">
+        <f>INDEX(Sale!E1:E16,MATCH(Answers!C121,Sale!A1:A16,0))</f>
+        <v>C005</v>
+      </c>
+    </row>
+    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B141" t="s">
+        <v>45</v>
+      </c>
+      <c r="C141" t="str">
+        <f>INDEX(Customer!B1:B12,MATCH(Answers!C140,Customer!A1:A12,0))</f>
+        <v>Arjun Singh</v>
+      </c>
+    </row>
+    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B142" t="s">
+        <v>46</v>
+      </c>
+      <c r="C142" t="str">
+        <f>INDEX(Customer!C1:C12,MATCH(Answers!C140,Customer!A1:A12,0))</f>
+        <v>Jaipur</v>
+      </c>
+    </row>
+    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B144" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B146" t="s">
+        <v>91</v>
+      </c>
+      <c r="C146" t="str">
+        <f>INDEX(Sale!J1:J16,MATCH(Answers!C121,Sale!A1:A16,0))</f>
+        <v>S005</v>
+      </c>
+    </row>
+    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B147" t="s">
+        <v>92</v>
+      </c>
+      <c r="C147" t="str">
+        <f>INDEX(Store!B1:B7,MATCH(Answers!C146,Store!A1:A7,0))</f>
+        <v>Smart World</v>
+      </c>
+    </row>
+    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B148" t="s">
+        <v>177</v>
+      </c>
+      <c r="C148" t="str">
+        <f>INDEX(Store!C1:C7,MATCH(Answers!C146,Store!A1:A7,0))</f>
+        <v>Jaipur</v>
       </c>
     </row>
   </sheetData>
@@ -10545,6 +10812,176 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C66404C-EC94-4A2A-8D51-91827D3C6706}">
+  <dimension ref="A1:A45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>194</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BE303A-7F11-4007-AB4F-EC495D2B0D40}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10758,7 +11195,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE4B28B0-A4E0-41F2-A448-151B266A0B3F}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10866,7 +11303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DACC2AA0-1BDF-4DAA-99B1-5D13A573DBF9}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
